--- a/check-gefei-kd/report/history/keyword-table-20260710-153032.xlsx
+++ b/check-gefei-kd/report/history/keyword-table-20260710-153032.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="keywords" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$L$2</definedName>
@@ -34,12 +34,22 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4EAFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -65,7 +75,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -541,16 +560,16 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -566,52 +585,52 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>score(simWindowVolume*cpc/kd)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sim)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sim)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sim)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>volume(sem)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>kd(sem)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cpc(sem)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>gefeiKD</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>sourcePresence(SIM/SEM)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>score(simWindowVolume*cpc/kd)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sim)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sim)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sim)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sem)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sem)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sem)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>gefeiKD</t>
         </is>
       </c>
     </row>
@@ -626,43 +645,33 @@
           <t>example.com</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="6" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="8" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>image to text
 image-to-text</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>sim_only（仅 SIM）</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="5" t="n"/>
-      <c r="K2" s="5" t="n"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>43.2</t>
         </is>
       </c>
     </row>
